--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_20_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_20_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9987E55-779D-4E30-AA8D-1D81CD1D1F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD7F6CF-EC34-4305-8170-91B0953DBFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,64 +55,40 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT OFSS 28 Aug 2025 8800 CE</t>
-  </si>
-  <si>
-    <t>25-08-2025</t>
-  </si>
-  <si>
-    <t>OPT JSWSTEEL 28 Aug 2025 1050 CE</t>
-  </si>
-  <si>
-    <t>OPT TATAELXSI 28 Aug 2025 5600 CE</t>
-  </si>
-  <si>
-    <t>OPT ZYDUSLIFE 28 Aug 2025 1000 PE</t>
-  </si>
-  <si>
-    <t>26-08-2025</t>
-  </si>
-  <si>
-    <t>OPT DIVISLAB 28 Aug 2025 6000 PE</t>
-  </si>
-  <si>
-    <t>OPT COLPAL 30 Sep 2025 2260 PE</t>
-  </si>
-  <si>
-    <t>28-08-2025</t>
-  </si>
-  <si>
-    <t>OPT BIOCON 30 Sep 2025 360 PE</t>
-  </si>
-  <si>
-    <t>OPT ADANIPORTS 30 Sep 2025 1320 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 28 Aug 2025 24600 CE</t>
-  </si>
-  <si>
-    <t>OPT DLF 30 Sep 2025 740 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 28 Aug 2025 24700 PE</t>
-  </si>
-  <si>
-    <t>OPT HINDUNILVR 30 Sep 2025 2600 CE</t>
-  </si>
-  <si>
-    <t>29-08-2025</t>
-  </si>
-  <si>
-    <t>OPT DABUR 30 Sep 2025 500 CE</t>
-  </si>
-  <si>
-    <t>OPT RBLBANK 30 Sep 2025 260 CE</t>
-  </si>
-  <si>
-    <t>OPT VBL 30 Sep 2025 480 CE</t>
-  </si>
-  <si>
-    <t>OPT TRENT 30 Sep 2025 5300 CE</t>
+    <t>OPT UNOMINDA 28 Oct 2025 1240 PE</t>
+  </si>
+  <si>
+    <t>14-10-2025</t>
+  </si>
+  <si>
+    <t>OPT PHOENIXLTD 28 Oct 2025 1640 CE</t>
+  </si>
+  <si>
+    <t>15-10-2025</t>
+  </si>
+  <si>
+    <t>OPT ICICIGI 28 Oct 2025 1960 CE</t>
+  </si>
+  <si>
+    <t>OPT SONACOMS 28 Oct 2025 460 CE</t>
+  </si>
+  <si>
+    <t>16-10-2025</t>
+  </si>
+  <si>
+    <t>OPT JIOFIN 28 Oct 2025 310 PE</t>
+  </si>
+  <si>
+    <t>17-10-2025</t>
+  </si>
+  <si>
+    <t>OPT TATACONSUM 28 Oct 2025 1150 CE</t>
+  </si>
+  <si>
+    <t>OPT PFC 28 Oct 2025 400 PE</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 28 Oct 2025 2560 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -465,10 +441,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -484,10 +460,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -496,10 +472,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -522,754 +498,378 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45894</v>
+        <v>45944</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>550</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>43.75</v>
       </c>
       <c r="F2">
-        <v>9675</v>
+        <v>24062.5</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>75</v>
+        <v>550</v>
       </c>
       <c r="I2">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="J2">
-        <v>11250</v>
+        <v>25300</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1575</v>
+        <v>1237.5</v>
       </c>
       <c r="M2">
-        <v>67.62</v>
+        <v>93.96</v>
       </c>
       <c r="N2">
-        <v>1507.38</v>
+        <v>1143.54</v>
       </c>
       <c r="O2">
-        <v>1575</v>
+        <v>1237.5</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>147</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45894</v>
+        <v>45945</v>
       </c>
       <c r="D3">
-        <v>675</v>
+        <v>350</v>
       </c>
       <c r="E3">
-        <v>14.7</v>
+        <v>54.65</v>
       </c>
       <c r="F3">
-        <v>9922.5</v>
+        <v>19127.5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>675</v>
+        <v>350</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>59.8</v>
       </c>
       <c r="J3">
-        <v>9450</v>
+        <v>20930</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>-472.5</v>
+        <v>1802.5</v>
       </c>
       <c r="M3">
-        <v>65.099999999999994</v>
+        <v>85.07</v>
       </c>
       <c r="N3">
-        <v>-537.6</v>
+        <v>1717.43</v>
       </c>
       <c r="O3">
-        <v>472.5</v>
+        <v>1802.5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>262</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45945</v>
+      </c>
+      <c r="D4">
+        <v>325</v>
+      </c>
+      <c r="E4">
+        <v>49.65</v>
+      </c>
+      <c r="F4">
+        <v>16136.25</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1">
-        <v>45894</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>77</v>
-      </c>
-      <c r="F4">
-        <v>7700</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="H4">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="I4">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="J4">
-        <v>5400</v>
+        <v>17485</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>-2300</v>
+        <v>1348.75</v>
       </c>
       <c r="M4">
-        <v>58.34</v>
+        <v>79.31</v>
       </c>
       <c r="N4">
-        <v>-2358.34</v>
+        <v>1269.44</v>
       </c>
       <c r="O4">
-        <v>2300</v>
+        <v>1348.75</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45895</v>
+        <v>45946</v>
       </c>
       <c r="D5">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="E5">
-        <v>10.199999999999999</v>
+        <v>19.25</v>
       </c>
       <c r="F5">
-        <v>9180</v>
+        <v>20212.5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="J5">
-        <v>13500</v>
+        <v>19635</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>4320</v>
+        <v>-577.5</v>
       </c>
       <c r="M5">
-        <v>69.78</v>
+        <v>84.96</v>
       </c>
       <c r="N5">
-        <v>4250.22</v>
+        <v>-662.46</v>
       </c>
       <c r="O5">
-        <v>4320</v>
+        <v>577.5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
-        <v>45895</v>
+        <v>45947</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>4700</v>
       </c>
       <c r="E6">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="F6">
-        <v>750</v>
+        <v>25380</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>4700</v>
       </c>
       <c r="I6">
-        <v>9.5</v>
+        <v>5.08</v>
       </c>
       <c r="J6">
-        <v>950</v>
+        <v>23852.5</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>200</v>
+        <v>-1527.5</v>
       </c>
       <c r="M6">
-        <v>48.86</v>
+        <v>139.71</v>
       </c>
       <c r="N6">
-        <v>151.13999999999999</v>
+        <v>-1667.21</v>
       </c>
       <c r="O6">
-        <v>200</v>
+        <v>1527.5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
-        <v>45897</v>
+        <v>45947</v>
       </c>
       <c r="D7">
-        <v>225</v>
+        <v>550</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>24.25</v>
       </c>
       <c r="F7">
-        <v>12375</v>
+        <v>13337.5</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H7">
-        <v>225</v>
+        <v>550</v>
       </c>
       <c r="I7">
-        <v>58.2</v>
+        <v>22.45</v>
       </c>
       <c r="J7">
-        <v>13095</v>
+        <v>12347.5</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>720</v>
+        <v>-990</v>
       </c>
       <c r="M7">
-        <v>71.38</v>
+        <v>70.75</v>
       </c>
       <c r="N7">
-        <v>648.62</v>
+        <v>-1060.75</v>
       </c>
       <c r="O7">
-        <v>720</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>47</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
-        <v>45897</v>
+        <v>45947</v>
       </c>
       <c r="D8">
-        <v>2500</v>
+        <v>1300</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="F8">
-        <v>30000</v>
+        <v>11115</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H8">
-        <v>2500</v>
+        <v>1300</v>
       </c>
       <c r="I8">
-        <v>11.45</v>
+        <v>8.15</v>
       </c>
       <c r="J8">
-        <v>28625</v>
+        <v>10595</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>-1375</v>
+        <v>-520</v>
       </c>
       <c r="M8">
-        <v>101.3</v>
+        <v>67.260000000000005</v>
       </c>
       <c r="N8">
-        <v>-1476.3</v>
+        <v>-587.26</v>
       </c>
       <c r="O8">
-        <v>1375</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
-        <v>45897</v>
+        <v>45947</v>
       </c>
       <c r="D9">
-        <v>475</v>
+        <v>300</v>
       </c>
       <c r="E9">
-        <v>46.6</v>
+        <v>49.85</v>
       </c>
       <c r="F9">
-        <v>22135</v>
+        <v>14955</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H9">
-        <v>475</v>
+        <v>300</v>
       </c>
       <c r="I9">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="J9">
-        <v>22372.5</v>
+        <v>13980</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>237.5</v>
+        <v>-975</v>
       </c>
       <c r="M9">
-        <v>88.94</v>
+        <v>74.08</v>
       </c>
       <c r="N9">
-        <v>148.56</v>
+        <v>-1049.08</v>
       </c>
       <c r="O9">
-        <v>237.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>189</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1">
-        <v>45897</v>
-      </c>
-      <c r="D10">
-        <v>75</v>
-      </c>
-      <c r="E10">
-        <v>83</v>
-      </c>
-      <c r="F10">
-        <v>6225</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10">
-        <v>75</v>
-      </c>
-      <c r="I10">
-        <v>63</v>
-      </c>
-      <c r="J10">
-        <v>4725</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>-1500</v>
-      </c>
-      <c r="M10">
-        <v>56.72</v>
-      </c>
-      <c r="N10">
-        <v>-1556.72</v>
-      </c>
-      <c r="O10">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>89</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1">
-        <v>45897</v>
-      </c>
-      <c r="D11">
-        <v>825</v>
-      </c>
-      <c r="E11">
-        <v>31.75</v>
-      </c>
-      <c r="F11">
-        <v>26193.75</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11">
-        <v>825</v>
-      </c>
-      <c r="I11">
-        <v>31.35</v>
-      </c>
-      <c r="J11">
-        <v>25863.75</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>-330</v>
-      </c>
-      <c r="M11">
-        <v>95.74</v>
-      </c>
-      <c r="N11">
-        <v>-425.74</v>
-      </c>
-      <c r="O11">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>193</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1">
-        <v>45897</v>
-      </c>
-      <c r="D12">
-        <v>75</v>
-      </c>
-      <c r="E12">
-        <v>85</v>
-      </c>
-      <c r="F12">
-        <v>6375</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12">
-        <v>75</v>
-      </c>
-      <c r="I12">
-        <v>83.75</v>
-      </c>
-      <c r="J12">
-        <v>6281.25</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>-93.75</v>
-      </c>
-      <c r="M12">
-        <v>58.99</v>
-      </c>
-      <c r="N12">
-        <v>-152.74</v>
-      </c>
-      <c r="O12">
-        <v>93.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>122</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1">
-        <v>45898</v>
-      </c>
-      <c r="D13">
-        <v>300</v>
-      </c>
-      <c r="E13">
-        <v>96.5</v>
-      </c>
-      <c r="F13">
-        <v>28950</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13">
-        <v>300</v>
-      </c>
-      <c r="I13">
-        <v>97.5</v>
-      </c>
-      <c r="J13">
-        <v>29250</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>300</v>
-      </c>
-      <c r="M13">
-        <v>101.79</v>
-      </c>
-      <c r="N13">
-        <v>198.21</v>
-      </c>
-      <c r="O13">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>70</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1">
-        <v>45898</v>
-      </c>
-      <c r="D14">
-        <v>1250</v>
-      </c>
-      <c r="E14">
-        <v>22.4</v>
-      </c>
-      <c r="F14">
-        <v>28000</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14">
-        <v>1250</v>
-      </c>
-      <c r="I14">
-        <v>24.25</v>
-      </c>
-      <c r="J14">
-        <v>30312.5</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>2312.5</v>
-      </c>
-      <c r="M14">
-        <v>102.87</v>
-      </c>
-      <c r="N14">
-        <v>2209.63</v>
-      </c>
-      <c r="O14">
-        <v>2312.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>243</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="1">
-        <v>45898</v>
-      </c>
-      <c r="D15">
-        <v>3175</v>
-      </c>
-      <c r="E15">
-        <v>14.05</v>
-      </c>
-      <c r="F15">
-        <v>44608.75</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15">
-        <v>3175</v>
-      </c>
-      <c r="I15">
-        <v>14.7</v>
-      </c>
-      <c r="J15">
-        <v>46672.5</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>2063.75</v>
-      </c>
-      <c r="M15">
-        <v>134.22999999999999</v>
-      </c>
-      <c r="N15">
-        <v>1929.52</v>
-      </c>
-      <c r="O15">
-        <v>2063.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>285</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="1">
-        <v>45898</v>
-      </c>
-      <c r="D16">
-        <v>1025</v>
-      </c>
-      <c r="E16">
-        <v>24</v>
-      </c>
-      <c r="F16">
-        <v>24600</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16">
-        <v>1025</v>
-      </c>
-      <c r="I16">
-        <v>22.45</v>
-      </c>
-      <c r="J16">
-        <v>23011.25</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>-1588.75</v>
-      </c>
-      <c r="M16">
-        <v>90.97</v>
-      </c>
-      <c r="N16">
-        <v>-1679.72</v>
-      </c>
-      <c r="O16">
-        <v>1588.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>282</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="1">
-        <v>45898</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>238.9</v>
-      </c>
-      <c r="F17">
-        <v>23890</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17">
-        <v>100</v>
-      </c>
-      <c r="I17">
-        <v>216</v>
-      </c>
-      <c r="J17">
-        <v>21600</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>-2290</v>
-      </c>
-      <c r="M17">
-        <v>88.65</v>
-      </c>
-      <c r="N17">
-        <v>-2378.65</v>
-      </c>
-      <c r="O17">
-        <v>2290</v>
+        <v>975</v>
       </c>
     </row>
   </sheetData>
